--- a/Day30_RAG_Intro/data/llamaparse_output/all_extracted_tables.xlsx
+++ b/Day30_RAG_Intro/data/llamaparse_output/all_extracted_tables.xlsx
@@ -22,9 +22,9 @@
     <sheet name="Appendix A- Complex -17" sheetId="17" r:id="rId17"/>
     <sheet name="Appendix B- Regional-18" sheetId="18" r:id="rId18"/>
     <sheet name="Appendix C- Invoice -19" sheetId="19" r:id="rId19"/>
-    <sheet name="Visual Appendix 2- C-20" sheetId="20" r:id="rId20"/>
-    <sheet name="Visual Appendix 2- C-21" sheetId="21" r:id="rId21"/>
-    <sheet name="SCANNED TAX INVOICE-22" sheetId="22" r:id="rId22"/>
+    <sheet name="Open Contract Risks -20" sheetId="20" r:id="rId20"/>
+    <sheet name="Open Contract Risks -21" sheetId="21" r:id="rId21"/>
+    <sheet name="Line Items-22" sheetId="22" r:id="rId22"/>
     <sheet name="Line Items-23" sheetId="23" r:id="rId23"/>
     <sheet name="Appendix I- Profile -24" sheetId="24" r:id="rId24"/>
   </sheets>
@@ -680,7 +680,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Time Slot</v>
+        <v/>
       </c>
       <c r="B1" t="str">
         <v>Mon</v>
@@ -1173,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1186,12 +1186,15 @@
         <v>Responsible Team</v>
       </c>
       <c r="D1" t="str">
+        <v>Responsible Team</v>
+      </c>
+      <c r="E1" t="str">
         <v>Trigger</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Evidence Required</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Risk</v>
       </c>
     </row>
@@ -1203,15 +1206,18 @@
         <v>Delete client data after contract termination unless retention is legally required.</v>
       </c>
       <c r="C2" t="str">
-        <v>Owner Compliance&lt;br/&gt;Backup Legal</v>
+        <v>Owner</v>
       </c>
       <c r="D2" t="str">
+        <v>Compliance</v>
+      </c>
+      <c r="E2" t="str">
         <v>Termination notice received</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Deletion certificate + audit log export</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>High</v>
       </c>
     </row>
@@ -1220,39 +1226,45 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>Notify client about any confirmed data incident within 72 hours.</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>Owner Security&lt;br/&gt;Backup DPO</v>
+        <v>Backup</v>
       </c>
       <c r="D3" t="str">
-        <v>Incident classified as confirmed breach</v>
+        <v>Legal</v>
       </c>
       <c r="E3" t="str">
-        <v>Incident report, timeline, notification proof</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>Critical</v>
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Billing</v>
+        <v/>
       </c>
       <c r="B4" t="str">
-        <v>Apply annual platform fee adjustment only after renewal confirmation.</v>
+        <v>Notify client about any confirmed data incident within 72 hours.</v>
       </c>
       <c r="C4" t="str">
-        <v>Owner Finance&lt;br/&gt;Backup CSM</v>
+        <v>Owner</v>
       </c>
       <c r="D4" t="str">
-        <v>Renewal order approved</v>
+        <v>Security</v>
       </c>
       <c r="E4" t="str">
-        <v>Approved renewal sheet + invoice draft</v>
+        <v>Incident classified as confirmed breach</v>
       </c>
       <c r="F4" t="str">
-        <v>Medium</v>
+        <v>Incident report, timeline, notification proof</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Critical</v>
       </c>
     </row>
     <row r="5">
@@ -1260,39 +1272,45 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>Do not bill inactive campuses during suspension period.</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>Owner Revenue Ops&lt;br/&gt;Backup Finance</v>
+        <v>Backup</v>
       </c>
       <c r="D5" t="str">
-        <v>Campus status = suspended</v>
+        <v>DPO</v>
       </c>
       <c r="E5" t="str">
-        <v>ERP campus status export</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>High</v>
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Support</v>
+        <v>Billing</v>
       </c>
       <c r="B6" t="str">
-        <v>Provide P1 response within 30 minutes during school operating hours.</v>
+        <v>Apply annual platform fee adjustment only after renewal confirmation.</v>
       </c>
       <c r="C6" t="str">
-        <v>Owner Support L2&lt;br/&gt;Backup Ops Manager</v>
+        <v>Owner</v>
       </c>
       <c r="D6" t="str">
-        <v>Ticket priority = P1</v>
+        <v>Finance</v>
       </c>
       <c r="E6" t="str">
-        <v>Ticket timestamps + agent assignment log</v>
+        <v>Renewal order approved</v>
       </c>
       <c r="F6" t="str">
-        <v>High</v>
+        <v>Approved renewal sheet + invoice draft</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="7">
@@ -1300,24 +1318,165 @@
         <v/>
       </c>
       <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>Backup</v>
+      </c>
+      <c r="D7" t="str">
+        <v>CSM</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>Do not bill inactive campuses during suspension period.</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Revenue Ops</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Campus status = suspended</v>
+      </c>
+      <c r="F8" t="str">
+        <v>ERP campus status export</v>
+      </c>
+      <c r="G8" t="str">
+        <v>High</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>Backup</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Support</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Provide P1 response within 30 minutes during school operating hours.</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Support L2</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Ticket priority = P1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Ticket timestamps + agent assignment log</v>
+      </c>
+      <c r="G10" t="str">
+        <v>High</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>Backup</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Ops Manager</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
         <v>Escalate unresolved P2 tickets after 4 business hours.</v>
       </c>
-      <c r="C7" t="str">
-        <v>Owner Support L1&lt;br/&gt;Backup Support L2</v>
-      </c>
-      <c r="D7" t="str">
+      <c r="C12" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Support L1</v>
+      </c>
+      <c r="E12" t="str">
         <v>Ticket age &gt; 4 business hours</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F12" t="str">
         <v>Escalation log</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G12" t="str">
         <v>Medium</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>Backup</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Support L2</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1392,7 +1551,7 @@
         <v>INR 0.38/message</v>
       </c>
       <c r="G3" t="str">
-        <v>50% advance + monthly usage</v>
+        <v>50% advance +&lt;br/&gt;monthly usage</v>
       </c>
     </row>
     <row r="4">
@@ -1480,7 +1639,7 @@
         <v>ERP Platform</v>
       </c>
       <c r="B2" t="str">
-        <v>Annual School360 Enterprise Subscription -&lt;br/&gt;12 campuses</v>
+        <v>Annual School360 Enterprise Subscription - 12 campuses</v>
       </c>
       <c r="C2" t="str">
         <v>1</v>
@@ -1503,7 +1662,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>Parent communication add-on - estimated&lt;br/&gt;message pack</v>
+        <v>Parent communication add-on - estimated message pack</v>
       </c>
       <c r="C3" t="str">
         <v>2,00,000 msgs</v>
@@ -1552,7 +1711,7 @@
         <v>Subtotal and taxes</v>
       </c>
       <c r="C5" t="str">
-        <v>\*</v>
+        <v>*</v>
       </c>
       <c r="D5" t="str">
         <v>INR 14,16,000</v>
@@ -1662,7 +1821,7 @@
         <v>Month</v>
       </c>
       <c r="B1" t="str">
-        <v>Open Risks</v>
+        <v>Open Contract Risks</v>
       </c>
     </row>
     <row r="2">
@@ -2434,7 +2593,7 @@
         <v>API Availability</v>
       </c>
       <c r="B2" t="str">
-        <v>P1 - complete&lt;br/&gt;outage</v>
+        <v>P1 - complete outage</v>
       </c>
       <c r="C2" t="str">
         <v>15 minutes</v>
@@ -2443,10 +2602,10 @@
         <v>4 hours</v>
       </c>
       <c r="E2" t="str">
-        <v>10 percent monthly&lt;br/&gt;fee credit</v>
+        <v>10 percent monthly fee credit</v>
       </c>
       <c r="F2" t="str">
-        <v>Monitoring logs and incident&lt;br/&gt;ticket</v>
+        <v>Monitoring logs and incident ticket</v>
       </c>
     </row>
     <row r="3">
@@ -2454,7 +2613,7 @@
         <v>API Availability</v>
       </c>
       <c r="B3" t="str">
-        <v>P2 - degraded&lt;br/&gt;performance</v>
+        <v>P2 - degraded performance</v>
       </c>
       <c r="C3" t="str">
         <v>30 minutes</v>
@@ -2463,10 +2622,10 @@
         <v>8 hours</v>
       </c>
       <c r="E3" t="str">
-        <v>5 percent monthly fee&lt;br/&gt;credit</v>
+        <v>5 percent monthly fee credit</v>
       </c>
       <c r="F3" t="str">
-        <v>Latency dashboard and&lt;br/&gt;affected endpoint list</v>
+        <v>Latency dashboard and affected endpoint list</v>
       </c>
     </row>
     <row r="4">
@@ -2474,7 +2633,7 @@
         <v>Data Pipeline</v>
       </c>
       <c r="B4" t="str">
-        <v>P1 - ingestion&lt;br/&gt;stopped</v>
+        <v>P1 - ingestion stopped</v>
       </c>
       <c r="C4" t="str">
         <v>20 minutes</v>
@@ -2483,10 +2642,10 @@
         <v>6 hours</v>
       </c>
       <c r="E4" t="str">
-        <v>8 percent pipeline fee&lt;br/&gt;credit</v>
+        <v>8 percent pipeline fee credit</v>
       </c>
       <c r="F4" t="str">
-        <v>Queue depth, failed job IDs,&lt;br/&gt;replay report</v>
+        <v>Queue depth, failed job IDs, replay report</v>
       </c>
     </row>
     <row r="5">
@@ -2494,7 +2653,7 @@
         <v>Data Pipeline</v>
       </c>
       <c r="B5" t="str">
-        <v>P3 - delayed&lt;br/&gt;batch</v>
+        <v>P3 - delayed batch</v>
       </c>
       <c r="C5" t="str">
         <v>4 hours</v>
@@ -2506,7 +2665,7 @@
         <v>No automatic credit</v>
       </c>
       <c r="F5" t="str">
-        <v>Batch ID and SLA exception&lt;br/&gt;note</v>
+        <v>Batch ID and SLA exception note</v>
       </c>
     </row>
     <row r="6">
@@ -2514,7 +2673,7 @@
         <v>Support</v>
       </c>
       <c r="B6" t="str">
-        <v>P2 - urgent&lt;br/&gt;support</v>
+        <v>P2 - urgent support</v>
       </c>
       <c r="C6" t="str">
         <v>1 hour</v>
@@ -2523,7 +2682,7 @@
         <v>1 business day</v>
       </c>
       <c r="E6" t="str">
-        <v>2 percent support fee&lt;br/&gt;credit</v>
+        <v>2 percent support fee credit</v>
       </c>
       <c r="F6" t="str">
         <v>Support ticket with timestamps</v>
